--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -810,9 +810,225 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136921994</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106406</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bålsta_NVI, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>644992</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6602970</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Upplands-Bro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Låssa</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>NVI_Sweco</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johannes Måsviken, Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136921994</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136922029</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106406</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bålsta_NVI, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>645042</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6602950</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Upplands-Bro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Låssa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>NVI_Sweco</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johannes Måsviken, Anton Ringbom</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922029</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106406</v>
+        <v>106412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106406</v>
+        <v>106412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106412</v>
+        <v>106414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106412</v>
+        <v>106414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106414</v>
+        <v>106415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106414</v>
+        <v>106415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106415</v>
+        <v>106421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106415</v>
+        <v>106421</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106421</v>
+        <v>106425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106421</v>
+        <v>106425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106425</v>
+        <v>106427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106425</v>
+        <v>106427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106427</v>
+        <v>106429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106427</v>
+        <v>106429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106429</v>
+        <v>106442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106429</v>
+        <v>106442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106442</v>
+        <v>106444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106442</v>
+        <v>106444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106444</v>
+        <v>106448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106444</v>
+        <v>106448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106448</v>
+        <v>106467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106448</v>
+        <v>106467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106467</v>
+        <v>106468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106467</v>
+        <v>106468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106468</v>
+        <v>106473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106468</v>
+        <v>106473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106473</v>
+        <v>106476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106473</v>
+        <v>106476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106476</v>
+        <v>106482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106476</v>
+        <v>106482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106483</v>
+        <v>106495</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106483</v>
+        <v>106495</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106495</v>
+        <v>106496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106495</v>
+        <v>106496</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 73773-2021 artfynd.xlsx
+++ b/artfynd/A 73773-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>136921994</v>
       </c>
       <c r="B3" t="n">
-        <v>106496</v>
+        <v>106499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136922029</v>
       </c>
       <c r="B4" t="n">
-        <v>106496</v>
+        <v>106499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
